--- a/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
+++ b/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
@@ -1,23 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/774010bec831de26/Códigos - Projeto TotalEnergies/Código_Pré_Modificações_Fred/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor\OneDrive\Documentos\Vitor\Projetos\PycharmProjects\Projeto_TotalEnergies\Código_Pré_Modificações_Fred\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{73FBDB56-E315-4256-A304-B2AFEEE3C4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3346991-845F-4D28-A31D-A5569B20F9D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5FFA92-C2DC-4444-B0F5-7874CA72DC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Yanes_P1" sheetId="4" r:id="rId1"/>
     <sheet name="Yanes_P2" sheetId="6" r:id="rId2"/>
     <sheet name="Yanes_P3" sheetId="7" r:id="rId3"/>
-    <sheet name="Tharanivasan_Lloydminster1" sheetId="8" r:id="rId4"/>
-    <sheet name="Tharanivasan_Lloydminster2" sheetId="9" r:id="rId5"/>
+    <sheet name="Alves_BR1_5C" sheetId="19" r:id="rId4"/>
+    <sheet name="Alves_BR1_25C" sheetId="11" r:id="rId5"/>
+    <sheet name="Alves_BR1_50C" sheetId="12" r:id="rId6"/>
+    <sheet name="Alves_BR2_5C" sheetId="13" r:id="rId7"/>
+    <sheet name="Alves_BR2_25C" sheetId="14" r:id="rId8"/>
+    <sheet name="Alves_BR2_50C" sheetId="15" r:id="rId9"/>
+    <sheet name="Alves_BR3_5C" sheetId="16" r:id="rId10"/>
+    <sheet name="Alves_BR3_25C" sheetId="17" r:id="rId11"/>
+    <sheet name="Alves_BR3_50C" sheetId="18" r:id="rId12"/>
+    <sheet name="Tharanivasan_Lloydminster_1" sheetId="8" r:id="rId13"/>
+    <sheet name="Tharanivasan_Lloydminster_2" sheetId="9" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="13">
   <si>
     <t>Saturados</t>
   </si>
@@ -77,16 +86,21 @@
   <si>
     <t>Yield_Exp</t>
   </si>
+  <si>
+    <t>DADOS DE YIELD OBTIDOS POR PLOT DIGITIZER</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.000000000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,8 +122,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF2C2C2C"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF2C2C2C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -119,6 +159,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -229,10 +281,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -291,9 +344,34 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -336,8 +414,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2286000" y="171450"/>
-          <a:ext cx="12068925" cy="5124814"/>
+          <a:off x="2339340" y="171450"/>
+          <a:ext cx="12068925" cy="4915264"/>
           <a:chOff x="2286000" y="209550"/>
           <a:chExt cx="12068925" cy="5334364"/>
         </a:xfrm>
@@ -771,514 +849,973 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>23073</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6728485B-563A-4D27-BC8D-90C3091FBD91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2476713"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94F341E6-56EA-4091-A797-7FACE19C5D71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6225540" y="1455420"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>600801</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>181339</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Agrupar 7">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572E572B-3A8B-D2E4-CF97-5E6EFF6B33AB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DC21CDF-4A4E-47E4-97AA-5683785EF26A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="2286000" y="142875"/>
-          <a:ext cx="11992701" cy="5410564"/>
-          <a:chOff x="2286000" y="200025"/>
-          <a:chExt cx="11992701" cy="5410564"/>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="14" name="Agrupar 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4E4B3CE-3F0A-D69F-F8A9-CAC5924B846E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="2286000" y="209550"/>
-            <a:ext cx="6706536" cy="5401039"/>
-            <a:chOff x="2286000" y="209550"/>
-            <a:chExt cx="6706536" cy="5401039"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="6" name="Imagem 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68B39BB4-5EEE-4CEE-80F2-3EB28F63E2FE}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2286000" y="209550"/>
-              <a:ext cx="5744377" cy="2705478"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="12" name="Imagem 11">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA4EF3DD-B82A-46FF-9EAE-361850296101}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2286000" y="3000375"/>
-              <a:ext cx="6706536" cy="2610214"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:pic>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="7" name="Agrupar 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B649B1-B8DB-ED08-961D-45EC137B4B15}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="9077325" y="200025"/>
-            <a:ext cx="5201376" cy="4105848"/>
-            <a:chOff x="9077325" y="200025"/>
-            <a:chExt cx="5201376" cy="4105848"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="2" name="Imagem 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45428B94-A495-7715-49BA-EC3DC243C847}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="9077325" y="200025"/>
-              <a:ext cx="5201376" cy="4105848"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="CaixaDeTexto 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ABA830A-A0A9-458A-8DE8-B481F48780C6}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="11582400" y="762000"/>
-              <a:ext cx="2476500" cy="542925"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="38100" cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="pt-BR" sz="1400"/>
-                <a:t>alpha e Mav são lidos no </a:t>
-              </a:r>
-            </a:p>
-            <a:p>
-              <a:r>
-                <a:rPr lang="pt-BR" sz="1400"/>
-                <a:t>'variáveis_entrada_código.txt'</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD3CA500-08BE-4977-A518-AA2DEFF3669F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>480454</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>99362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F1903E-6244-4C5A-BA70-45D5A0ADE4A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8442960" y="83820"/>
+          <a:ext cx="4549534" cy="3490262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38313</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{253741E0-502D-4BA8-8CF8-60130B72CB39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2491953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F95758E-B08D-44F6-A382-2AB35C3EA5E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6225540" y="1455420"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>410292</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>76774</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="9" name="Agrupar 8">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DCAB56A-8067-2229-47A3-FB5261CA182C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E6D2137-FEB5-4643-AA53-7D0229895C69}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="2238375" y="161925"/>
-          <a:ext cx="12459417" cy="4124899"/>
-          <a:chOff x="2276475" y="133350"/>
-          <a:chExt cx="12459417" cy="4124899"/>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="3" name="Agrupar 2">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFE14E4D-6100-FAD2-5BC2-08BC4B28C2BA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="2276475" y="133350"/>
-            <a:ext cx="7258050" cy="3486150"/>
-            <a:chOff x="2276475" y="200025"/>
-            <a:chExt cx="7258050" cy="3505200"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="8" name="Imagem 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAF3EF19-2543-4BB4-9F65-F53BA4259F49}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2286000" y="200025"/>
-              <a:ext cx="6106559" cy="2817808"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2" name="CaixaDeTexto 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E40A26F-D442-4FFC-B1CF-75A7E6EB2EC5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2276475" y="3086100"/>
-              <a:ext cx="7258050" cy="619125"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:schemeClr val="bg1">
-                <a:lumMod val="95000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="12700" cmpd="sng">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="pt-BR" sz="1600"/>
-                <a:t>Dados de yields não disponíveis na dissertação</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="pt-BR" sz="1600" baseline="0"/>
-                <a:t> nem</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="pt-BR" sz="1600"/>
-                <a:t> no artigo de Yanes (2018)</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="7" name="Agrupar 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC336097-0A00-75E4-DE62-086F8BC81710}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="9601200" y="142875"/>
-            <a:ext cx="5134692" cy="4115374"/>
-            <a:chOff x="9829800" y="314325"/>
-            <a:chExt cx="5134692" cy="4115374"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="5" name="Imagem 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D055422C-6E4B-3EED-8CCD-B9EF5939D517}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="9829800" y="314325"/>
-              <a:ext cx="5134692" cy="4115374"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="CaixaDeTexto 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{324B237D-C0C0-46CB-88D8-1E39C6A06D63}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="12249150" y="895350"/>
-              <a:ext cx="2476500" cy="542925"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="38100" cmpd="sng">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="pt-BR" sz="1400"/>
-                <a:t>alpha e Mav são lidos no </a:t>
-              </a:r>
-            </a:p>
-            <a:p>
-              <a:r>
-                <a:rPr lang="pt-BR" sz="1400"/>
-                <a:t>'variáveis_entrada_código.txt'</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5866AE6-7F85-48F8-AEBA-5525B84014B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>480454</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114602</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D80147D4-9512-4611-A0FC-D32407821FD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8442960" y="83820"/>
+          <a:ext cx="4549534" cy="3505502"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38313</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E73C2AA-C304-4D83-900C-4E44592AE9E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2491953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BF5FA6F-551E-4AC7-A22C-D9767AD4490D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6225540" y="1455420"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2957ECEC-85D8-4127-972A-E594F6F7583F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{585BB59F-1CD1-424B-9433-1BBDB7A95529}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>480454</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114602</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5DB8F4B-0513-4FFF-81D7-60D6C90C4511}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8442960" y="83820"/>
+          <a:ext cx="4549534" cy="3505502"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1306,8 +1843,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2190749" y="85725"/>
-          <a:ext cx="13402605" cy="5238750"/>
+          <a:off x="2244089" y="85725"/>
+          <a:ext cx="13402605" cy="5029200"/>
           <a:chOff x="2247899" y="161925"/>
           <a:chExt cx="13402605" cy="5238750"/>
         </a:xfrm>
@@ -1720,7 +2257,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1748,8 +2285,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2190750" y="85725"/>
-          <a:ext cx="13402605" cy="5238750"/>
+          <a:off x="2244090" y="85725"/>
+          <a:ext cx="13402605" cy="5029200"/>
           <a:chOff x="2247899" y="161925"/>
           <a:chExt cx="13402605" cy="5238750"/>
         </a:xfrm>
@@ -2162,6 +2699,3117 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>600801</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>181339</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="8" name="Agrupar 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{572E572B-3A8B-D2E4-CF97-5E6EFF6B33AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2339340" y="142875"/>
+          <a:ext cx="11992701" cy="5189584"/>
+          <a:chOff x="2286000" y="200025"/>
+          <a:chExt cx="11992701" cy="5410564"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="14" name="Agrupar 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4E4B3CE-3F0A-D69F-F8A9-CAC5924B846E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2286000" y="209550"/>
+            <a:ext cx="6706536" cy="5401039"/>
+            <a:chOff x="2286000" y="209550"/>
+            <a:chExt cx="6706536" cy="5401039"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="Imagem 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68B39BB4-5EEE-4CEE-80F2-3EB28F63E2FE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2286000" y="209550"/>
+              <a:ext cx="5744377" cy="2705478"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="12" name="Imagem 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA4EF3DD-B82A-46FF-9EAE-361850296101}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2286000" y="3000375"/>
+              <a:ext cx="6706536" cy="2610214"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="Agrupar 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49B649B1-B8DB-ED08-961D-45EC137B4B15}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="9077325" y="200025"/>
+            <a:ext cx="5201376" cy="4105848"/>
+            <a:chOff x="9077325" y="200025"/>
+            <a:chExt cx="5201376" cy="4105848"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="Imagem 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45428B94-A495-7715-49BA-EC3DC243C847}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9077325" y="200025"/>
+              <a:ext cx="5201376" cy="4105848"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ABA830A-A0A9-458A-8DE8-B481F48780C6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11582400" y="762000"/>
+              <a:ext cx="2476500" cy="542925"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100" cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1400"/>
+                <a:t>alpha e Mav são lidos no </a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1400"/>
+                <a:t>'variáveis_entrada_código.txt'</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>410292</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="9" name="Agrupar 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DCAB56A-8067-2229-47A3-FB5261CA182C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2291715" y="161925"/>
+          <a:ext cx="12459417" cy="3145155"/>
+          <a:chOff x="2276475" y="133350"/>
+          <a:chExt cx="12459417" cy="4124899"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="3" name="Agrupar 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFE14E4D-6100-FAD2-5BC2-08BC4B28C2BA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2276475" y="133350"/>
+            <a:ext cx="7258050" cy="3486150"/>
+            <a:chOff x="2276475" y="200025"/>
+            <a:chExt cx="7258050" cy="3505200"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="Imagem 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAF3EF19-2543-4BB4-9F65-F53BA4259F49}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2286000" y="200025"/>
+              <a:ext cx="6106559" cy="2817808"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2" name="CaixaDeTexto 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E40A26F-D442-4FFC-B1CF-75A7E6EB2EC5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2276475" y="3086100"/>
+              <a:ext cx="7258050" cy="619125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1600"/>
+                <a:t>Dados de yields não disponíveis na dissertação</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1600" baseline="0"/>
+                <a:t> nem</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1600"/>
+                <a:t> no artigo de Yanes (2018)</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="Agrupar 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC336097-0A00-75E4-DE62-086F8BC81710}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="9601200" y="142875"/>
+            <a:ext cx="5134692" cy="4115374"/>
+            <a:chOff x="9829800" y="314325"/>
+            <a:chExt cx="5134692" cy="4115374"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="Imagem 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D055422C-6E4B-3EED-8CCD-B9EF5939D517}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9829800" y="314325"/>
+              <a:ext cx="5134692" cy="4115374"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6" name="CaixaDeTexto 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{324B237D-C0C0-46CB-88D8-1E39C6A06D63}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="12249150" y="895350"/>
+              <a:ext cx="2476500" cy="542925"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="38100" cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1400"/>
+                <a:t>alpha e Mav são lidos no </a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1400"/>
+                <a:t>'variáveis_entrada_código.txt'</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>115103</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>68</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{079B6E6F-9F95-41F2-94C9-66F1C7044302}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2606040" y="5404485"/>
+          <a:ext cx="5753903" cy="462983"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76353</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152514</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2DFBA10-67FF-4FA8-B50C-7D131FB50800}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8444865" y="5231130"/>
+          <a:ext cx="1095528" cy="788784"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09F69518-150A-4831-B754-1CB804864B37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2510789" y="5154930"/>
+          <a:ext cx="7124701" cy="962025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CaixaDeTexto 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13270192-AB3F-4B0E-BA7F-442B546717D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9721215" y="5240655"/>
+          <a:ext cx="2914650" cy="807720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>Yield_exp e SARA extraídos do código MATLAB no apendice da dissertação do Romero</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>175473</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6FC7961-E4E9-4B20-99ED-022C68B9A69C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2461473"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3908157-72FF-4152-A9A4-6D405436D575}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4541520" y="1440180"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ADE121B-7719-4E2F-8AF8-730783A8AC2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2062A3FF-F7A4-43D0-A0A3-0C4F26B2ACDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>526180</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38407</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAD4A420-4A3F-45CB-8026-D5D4753A36DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8427720" y="167640"/>
+          <a:ext cx="4610500" cy="3543607"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>115103</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>68</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A10D00C-5A00-480F-B3E1-3C67C6F97B9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2606040" y="5404485"/>
+          <a:ext cx="5753903" cy="462983"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76353</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152514</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71B9DA0C-8AE4-4F2F-ADA3-2BBBD8918329}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8444865" y="5231130"/>
+          <a:ext cx="1095528" cy="788784"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8BECD07-BEFE-4F81-A069-82E997A1131E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2510789" y="5154930"/>
+          <a:ext cx="7124701" cy="962025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CaixaDeTexto 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ACC2386-FB57-46DC-9643-BE1652221C38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9721215" y="5240655"/>
+          <a:ext cx="2914650" cy="807720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>Yield_exp e SARA extraídos do código MATLAB no apendice da dissertação do Romero</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87354BBD-771A-4134-9328-1F4B3C73CCD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2461473"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA94CE9F-D2A9-4424-A553-254CB6A8F96A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4541520" y="1440180"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1687E2A6-A587-4EAB-B5DE-F34974D877A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD32F651-79B6-4079-B938-95D8D3392A5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>526180</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>53647</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B058DFD1-5097-4826-BD25-CCF65CBA03BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8427720" y="167640"/>
+          <a:ext cx="4610500" cy="3543607"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>115103</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>68</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D08668B3-50F5-4464-9562-1BCDF9743D37}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2606040" y="5404485"/>
+          <a:ext cx="5753903" cy="462983"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76353</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152514</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D95E031B-6773-42B0-B6C7-8692FD55B1C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8444865" y="5231130"/>
+          <a:ext cx="1095528" cy="788784"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>361949</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EC27833-ABF0-472D-80A1-C3860F82CFF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2510789" y="5154930"/>
+          <a:ext cx="7124701" cy="962025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="CaixaDeTexto 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E2BB25B-0ED2-4736-978D-7E81293B89BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9721215" y="5240655"/>
+          <a:ext cx="2914650" cy="807720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>Yield_exp e SARA extraídos do código MATLAB no apendice da dissertação do Romero</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>23073</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{664B0C3C-45B6-462A-A217-76B129D7269B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2476713"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41CAAC0A-C8AB-4641-B7DF-23261B88A367}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4541520" y="1440180"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5868881A-46F0-4B64-8A58-964006171E05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78CD27A0-220B-4977-AEAC-BFD31F93A6F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>526180</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>68887</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagem 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA407FFC-52D5-480D-9A6B-3A4206B4FF24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8427720" y="167640"/>
+          <a:ext cx="4610500" cy="3558847"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7833</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E337E06E-DACE-4629-9BAE-C0EAF07AEE02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2461473"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D24635E8-8587-43A7-A831-C65C4BA9089C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5372100" y="1440180"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C92BA450-9BD1-4CED-A451-2836EE68149D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CF44494-CE05-4E05-B728-CE77F5F50BE8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>480454</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>84122</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagem 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F40F1747-9262-41E7-A5CC-4E480D1A1583}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8442960" y="83820"/>
+          <a:ext cx="4549534" cy="3490262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>23073</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F201C1-DAD5-4E00-9E99-5E2B1BC69FB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2476713"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1371BA5A-6EF6-4DAF-A31F-806C78F8C371}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5356860" y="1440180"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC28A06F-187F-439A-A2E8-7A8185F3BD1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5BCCAA0-35B2-4AAA-8018-CE4EE0650918}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>503314</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>175562</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagem 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{706E2D57-108D-4D20-ADD1-64F09DC47B34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8465820" y="175260"/>
+          <a:ext cx="4549534" cy="3490262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434725</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38313</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19CDF3F3-741B-49F6-93B1-20B139809140}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2407920" y="106680"/>
+          <a:ext cx="4442845" cy="2507193"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D29A069E-25E4-4258-9050-1F30F41EBB9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5356860" y="1463040"/>
+          <a:ext cx="571500" cy="830580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171066</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D736D77-06CB-40F6-B469-7F93165F7A3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2362200" y="2705100"/>
+          <a:ext cx="5280660" cy="590166"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1600"/>
+            <a:t>Dados de yields não disponíveis no artigo de Alves (2019)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>135255</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>134507</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="CaixaDeTexto 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99759AC7-3A1D-477C-9B18-E0DE9FFD8889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9599295" y="3807347"/>
+          <a:ext cx="2476500" cy="600300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="38100" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400"/>
+            <a:t>alpha e Mavg não fornecidos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>8014</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>129842</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagem 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A131B2E-5D8D-8DD1-5513-E39856335395}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8580120" y="129540"/>
+          <a:ext cx="4549534" cy="3490262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2425,13 +6073,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A864EB85-C00D-4DDE-AA79-FCAA285160FB}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -2439,7 +6087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2447,7 +6095,7 @@
         <v>31.726299999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -2455,7 +6103,7 @@
         <v>27.2151</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2463,7 +6111,7 @@
         <v>34.716700000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2471,7 +6119,7 @@
         <v>6.3418999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2479,7 +6127,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -2487,7 +6135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -2495,7 +6143,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
         <v>0.65035395900000004</v>
       </c>
@@ -2503,7 +6151,7 @@
         <v>5.1863426300000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="19">
         <v>0.70030734299999997</v>
       </c>
@@ -2511,7 +6159,7 @@
         <v>1.6792674100000002E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
         <v>0.75092592599999997</v>
       </c>
@@ -2519,7 +6167,7 @@
         <v>3.0681536559999997E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="19">
         <v>0.81134431200000001</v>
       </c>
@@ -2527,7 +6175,7 @@
         <v>4.4242223689999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="19">
         <v>0.85</v>
       </c>
@@ -2535,13 +6183,73 @@
         <v>5.4065000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
         <v>0.90012062800000003</v>
       </c>
       <c r="B14" s="14">
         <v>5.9044938299999995E-2</v>
       </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="24"/>
+      <c r="B20" s="23"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
+      <c r="B21" s="23"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="24"/>
+      <c r="B22" s="23"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="24"/>
+      <c r="B23" s="23"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="24"/>
+      <c r="B24" s="23"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="24"/>
+      <c r="B25" s="23"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="25"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="25"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="25"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="25"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="25"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="25"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="25"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
@@ -2555,15 +6263,1430 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0BAF0A3-1C7C-41EF-A94F-B0D60B70FFD6}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>273.15+5</f>
+        <v>278.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.69972823133484496</v>
+      </c>
+      <c r="B9" s="19">
+        <v>1.1475296952286199E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.74945654041487597</v>
+      </c>
+      <c r="B10" s="19">
+        <v>9.8361028220004501E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.79918478729875797</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1.1475296952286199E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.85054344403608595</v>
+      </c>
+      <c r="B12" s="19">
+        <v>1.9836068774612199E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.87010867325817998</v>
+      </c>
+      <c r="B13" s="19">
+        <v>2.9016393886867799E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.89945654818939502</v>
+      </c>
+      <c r="B14" s="19">
+        <v>4.7213112191146697E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{90D1CEA8-6C6A-47A3-8775-E4F2DA142BC5}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{963A2E9D-0D4F-44E1-A9D2-2E0AF9868D77}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>273.15+25</f>
+        <v>298.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.69891302640812203</v>
+      </c>
+      <c r="B9" s="19">
+        <v>2.45901632509723E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.74945654041487597</v>
+      </c>
+      <c r="B10" s="19">
+        <v>1.4754122964991E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.79918478729875797</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1.4754122964991E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.84972823910936301</v>
+      </c>
+      <c r="B12" s="19">
+        <v>9.8360653003889704E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.87010867325817998</v>
+      </c>
+      <c r="B13" s="19">
+        <v>2.21311469258752E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.90108695804284</v>
+      </c>
+      <c r="B14" s="19">
+        <v>3.8852459187256799E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{F5AD9CFD-55C0-493F-AA7C-898DD943EAF7}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFD8EBD6-13AB-410A-9E10-40E13FE53CB8}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>273.15+50</f>
+        <v>323.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.70461958528748003</v>
+      </c>
+      <c r="B9" s="19">
+        <v>3.1147565132306002E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.74864127329200403</v>
+      </c>
+      <c r="B10" s="19">
+        <v>4.7541007299621097E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.80407607905524403</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1.1475296952286199E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.84972823910936301</v>
+      </c>
+      <c r="B12" s="19">
+        <v>3.44262660729728E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.87010867325817998</v>
+      </c>
+      <c r="B13" s="19">
+        <v>1.22950816254862E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.90027169091996795</v>
+      </c>
+      <c r="B14" s="19">
+        <v>1.8032786384046401E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{09969C89-4EE5-4E9B-83D4-AC82878AF421}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D94E3C-228A-404B-AAAA-84368A7243B9}">
+  <dimension ref="A1:B52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>23+273.15</f>
+        <v>296.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>0.52</v>
+      </c>
+      <c r="B9" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
+        <v>0.53</v>
+      </c>
+      <c r="B10" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
+        <v>0.54</v>
+      </c>
+      <c r="B11" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="B12" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B13" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="B14" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="B15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
+        <v>0.59000000000000008</v>
+      </c>
+      <c r="B16" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="16">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="B17" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
+        <v>0.6100000000000001</v>
+      </c>
+      <c r="B18" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="16">
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="B19" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="16">
+        <v>0.63000000000000012</v>
+      </c>
+      <c r="B20" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="16">
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="B21" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="16">
+        <v>0.65000000000000013</v>
+      </c>
+      <c r="B22" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="16">
+        <v>0.66000000000000014</v>
+      </c>
+      <c r="B23" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
+        <v>0.67000000000000015</v>
+      </c>
+      <c r="B24" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="16">
+        <v>0.68000000000000016</v>
+      </c>
+      <c r="B25" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
+        <v>0.69000000000000017</v>
+      </c>
+      <c r="B26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="16">
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="B27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="16">
+        <v>0.71000000000000019</v>
+      </c>
+      <c r="B28" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="16">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="B29" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="16">
+        <v>0.7300000000000002</v>
+      </c>
+      <c r="B30" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="16">
+        <v>0.74000000000000021</v>
+      </c>
+      <c r="B31" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="16">
+        <v>0.75000000000000022</v>
+      </c>
+      <c r="B32" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="16">
+        <v>0.76000000000000023</v>
+      </c>
+      <c r="B33" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="16">
+        <v>0.77000000000000024</v>
+      </c>
+      <c r="B34" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="16">
+        <v>0.78000000000000025</v>
+      </c>
+      <c r="B35" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="16">
+        <v>0.79000000000000026</v>
+      </c>
+      <c r="B36" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="16">
+        <v>0.80000000000000027</v>
+      </c>
+      <c r="B37" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="16">
+        <v>0.81000000000000028</v>
+      </c>
+      <c r="B38" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="16">
+        <v>0.82000000000000028</v>
+      </c>
+      <c r="B39" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="16">
+        <v>0.83000000000000029</v>
+      </c>
+      <c r="B40" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="16">
+        <v>0.8400000000000003</v>
+      </c>
+      <c r="B41" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="16">
+        <v>0.85000000000000031</v>
+      </c>
+      <c r="B42" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="16">
+        <v>0.86000000000000032</v>
+      </c>
+      <c r="B43" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="16">
+        <v>0.87000000000000033</v>
+      </c>
+      <c r="B44" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="16">
+        <v>0.88000000000000034</v>
+      </c>
+      <c r="B45" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="16">
+        <v>0.89000000000000035</v>
+      </c>
+      <c r="B46" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="16">
+        <v>0.90000000000000036</v>
+      </c>
+      <c r="B47" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="16">
+        <v>0.91000000000000036</v>
+      </c>
+      <c r="B48" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="16">
+        <v>0.92000000000000037</v>
+      </c>
+      <c r="B49" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="16">
+        <v>0.93000000000000038</v>
+      </c>
+      <c r="B50" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="16">
+        <v>0.94000000000000039</v>
+      </c>
+      <c r="B51" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="16">
+        <v>0.9500000000000004</v>
+      </c>
+      <c r="B52" s="17">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{2A74D785-ECF9-41EC-83E7-D06BFD039F5C}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E17C7ABB-BD74-4BD8-89A4-BE9C8A53E418}">
+  <dimension ref="A1:B60"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <v>296.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>0.44</v>
+      </c>
+      <c r="B9" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
+        <v>0.45</v>
+      </c>
+      <c r="B10" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
+        <v>0.46</v>
+      </c>
+      <c r="B11" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="B12" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
+        <v>0.48000000000000004</v>
+      </c>
+      <c r="B13" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
+        <v>0.49000000000000005</v>
+      </c>
+      <c r="B14" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="B15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
+        <v>0.51</v>
+      </c>
+      <c r="B16" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="16">
+        <v>0.52</v>
+      </c>
+      <c r="B17" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
+        <v>0.53</v>
+      </c>
+      <c r="B18" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="16">
+        <v>0.54</v>
+      </c>
+      <c r="B19" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="B20" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="16">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B21" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="16">
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="B22" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="16">
+        <v>0.58000000000000007</v>
+      </c>
+      <c r="B23" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
+        <v>0.59000000000000008</v>
+      </c>
+      <c r="B24" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="16">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="B25" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
+        <v>0.6100000000000001</v>
+      </c>
+      <c r="B26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="16">
+        <v>0.62000000000000011</v>
+      </c>
+      <c r="B27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="16">
+        <v>0.63000000000000012</v>
+      </c>
+      <c r="B28" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="16">
+        <v>0.64000000000000012</v>
+      </c>
+      <c r="B29" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="16">
+        <v>0.65000000000000013</v>
+      </c>
+      <c r="B30" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="16">
+        <v>0.66000000000000014</v>
+      </c>
+      <c r="B31" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="16">
+        <v>0.67000000000000015</v>
+      </c>
+      <c r="B32" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="16">
+        <v>0.68000000000000016</v>
+      </c>
+      <c r="B33" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="16">
+        <v>0.69000000000000017</v>
+      </c>
+      <c r="B34" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="16">
+        <v>0.70000000000000018</v>
+      </c>
+      <c r="B35" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="16">
+        <v>0.71000000000000019</v>
+      </c>
+      <c r="B36" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="16">
+        <v>0.7200000000000002</v>
+      </c>
+      <c r="B37" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="16">
+        <v>0.7300000000000002</v>
+      </c>
+      <c r="B38" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="16">
+        <v>0.74000000000000021</v>
+      </c>
+      <c r="B39" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="16">
+        <v>0.75000000000000022</v>
+      </c>
+      <c r="B40" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="16">
+        <v>0.76000000000000023</v>
+      </c>
+      <c r="B41" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="16">
+        <v>0.77000000000000024</v>
+      </c>
+      <c r="B42" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="16">
+        <v>0.78000000000000025</v>
+      </c>
+      <c r="B43" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="16">
+        <v>0.79000000000000026</v>
+      </c>
+      <c r="B44" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="16">
+        <v>0.80000000000000027</v>
+      </c>
+      <c r="B45" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="16">
+        <v>0.81000000000000028</v>
+      </c>
+      <c r="B46" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="16">
+        <v>0.82000000000000028</v>
+      </c>
+      <c r="B47" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="16">
+        <v>0.83000000000000029</v>
+      </c>
+      <c r="B48" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="16">
+        <v>0.8400000000000003</v>
+      </c>
+      <c r="B49" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="16">
+        <v>0.85000000000000031</v>
+      </c>
+      <c r="B50" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="16">
+        <v>0.86000000000000032</v>
+      </c>
+      <c r="B51" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="16">
+        <v>0.87000000000000033</v>
+      </c>
+      <c r="B52" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="16">
+        <v>0.88000000000000034</v>
+      </c>
+      <c r="B53" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="16">
+        <v>0.89000000000000035</v>
+      </c>
+      <c r="B54" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="16">
+        <v>0.90000000000000036</v>
+      </c>
+      <c r="B55" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="16">
+        <v>0.91000000000000036</v>
+      </c>
+      <c r="B56" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="16">
+        <v>0.92000000000000037</v>
+      </c>
+      <c r="B57" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="16">
+        <v>0.93000000000000038</v>
+      </c>
+      <c r="B58" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="16">
+        <v>0.94000000000000039</v>
+      </c>
+      <c r="B59" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="16">
+        <v>0.9500000000000004</v>
+      </c>
+      <c r="B60" s="17">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{9887C3D9-0565-4471-929F-C8627F7789A8}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456DD2F0-32CF-464D-8480-E0EACECA597C}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -2571,7 +7694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2579,7 +7702,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -2587,7 +7710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2595,7 +7718,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2603,7 +7726,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2611,7 +7734,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -2619,7 +7742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -2627,7 +7750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>0.55000000000000004</v>
       </c>
@@ -2635,7 +7758,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>0.6</v>
       </c>
@@ -2643,7 +7766,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>0.65</v>
       </c>
@@ -2651,7 +7774,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>0.7</v>
       </c>
@@ -2659,7 +7782,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>0.75</v>
       </c>
@@ -2667,7 +7790,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>0.8</v>
       </c>
@@ -2675,7 +7798,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>0.85</v>
       </c>
@@ -2683,7 +7806,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>0.9</v>
       </c>
@@ -2705,13 +7828,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1797512-EA24-4634-8E9F-DFB374DA6616}">
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -2719,7 +7842,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2727,7 +7850,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -2735,7 +7858,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -2743,7 +7866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
@@ -2751,7 +7874,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -2759,7 +7882,7 @@
         <v>298.14999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -2767,7 +7890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -2775,215 +7898,97 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
-        <v>0.65</v>
-      </c>
-      <c r="B9" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
-        <v>0.66</v>
-      </c>
-      <c r="B10" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
-        <v>0.67</v>
-      </c>
-      <c r="B11" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="B12" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
-        <v>0.69000000000000006</v>
-      </c>
-      <c r="B13" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="B14" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
-        <v>0.71000000000000008</v>
-      </c>
-      <c r="B15" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
-        <v>0.72000000000000008</v>
-      </c>
-      <c r="B16" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
-        <v>0.73000000000000009</v>
-      </c>
-      <c r="B17" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
-        <v>0.7400000000000001</v>
-      </c>
-      <c r="B18" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
-        <v>0.75000000000000011</v>
-      </c>
-      <c r="B19" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
-        <v>0.76000000000000012</v>
-      </c>
-      <c r="B20" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
-        <v>0.77000000000000013</v>
-      </c>
-      <c r="B21" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
-        <v>0.78000000000000014</v>
-      </c>
-      <c r="B22" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
-        <v>0.79000000000000015</v>
-      </c>
-      <c r="B23" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
-        <v>0.80000000000000016</v>
-      </c>
-      <c r="B24" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
-        <v>0.81000000000000016</v>
-      </c>
-      <c r="B25" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
-        <v>0.82000000000000017</v>
-      </c>
-      <c r="B26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
-        <v>0.83000000000000018</v>
-      </c>
-      <c r="B27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
-        <v>0.84000000000000019</v>
-      </c>
-      <c r="B28" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
-        <v>0.8500000000000002</v>
-      </c>
-      <c r="B29" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
-        <v>0.86000000000000021</v>
-      </c>
-      <c r="B30" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
-        <v>0.87000000000000022</v>
-      </c>
-      <c r="B31" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
-        <v>0.88000000000000023</v>
-      </c>
-      <c r="B32" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
-        <v>0.89000000000000024</v>
-      </c>
-      <c r="B33" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
-        <v>0.90000000000000024</v>
-      </c>
-      <c r="B34" s="17">
-        <v>0</v>
-      </c>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="22">
+        <v>0.40307503049059501</v>
+      </c>
+      <c r="B9" s="22">
+        <v>5.42635650891516E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="22">
+        <v>0.50086103293641204</v>
+      </c>
+      <c r="B10" s="22">
+        <v>5.42635650891516E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
+        <v>0.59926200863547896</v>
+      </c>
+      <c r="B11" s="22">
+        <v>6.5116112507722596E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="22">
+        <v>0.65153752697560796</v>
+      </c>
+      <c r="B12" s="22">
+        <v>7.5969487922587298E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="22">
+        <v>0.69950797447615798</v>
+      </c>
+      <c r="B13" s="22">
+        <v>7.5969487922587298E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="22">
+        <v>0.74993850267467499</v>
+      </c>
+      <c r="B14" s="22">
+        <v>7.5969487922587298E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="22">
+        <v>0.74993850267467499</v>
+      </c>
+      <c r="B15" s="22">
+        <v>7.5969487922587298E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="22">
+        <v>0.799138990524208</v>
+      </c>
+      <c r="B16" s="22">
+        <v>3.36433937953477E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="22">
+        <v>0.85018446851535401</v>
+      </c>
+      <c r="B17" s="22">
+        <v>6.5116278106980997E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="22">
+        <v>0.89877000657225803</v>
+      </c>
+      <c r="B18" s="22">
+        <v>1.0418602841124299E-2</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D18:H18"/>
+  </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{D6508D5C-EDB0-4444-9F54-9DBB4E47E2F2}">
       <formula1>"n-heptano, n-pentano"</formula1>
@@ -2996,14 +8001,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D94E3C-228A-404B-AAAA-84368A7243B9}">
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE9846E-4BE6-48C3-91DB-C7394031C673}">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3011,47 +8016,48 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31.726299999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="5">
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27.2151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>34.716700000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.3418999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14">
-        <v>296.14999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <f>273.15+5</f>
+        <v>278.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
@@ -3059,7 +8065,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -3067,379 +8073,126 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
-        <v>0.52</v>
-      </c>
-      <c r="B9" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
-        <v>0.53</v>
-      </c>
-      <c r="B10" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
-        <v>0.54</v>
-      </c>
-      <c r="B11" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="B12" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B13" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="B14" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
-        <v>0.58000000000000007</v>
-      </c>
-      <c r="B15" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="B16" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="B17" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
-        <v>0.6100000000000001</v>
-      </c>
-      <c r="B18" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
-        <v>0.62000000000000011</v>
-      </c>
-      <c r="B19" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
-        <v>0.63000000000000012</v>
-      </c>
-      <c r="B20" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
-        <v>0.64000000000000012</v>
-      </c>
-      <c r="B21" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
-        <v>0.65000000000000013</v>
-      </c>
-      <c r="B22" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
-        <v>0.66000000000000014</v>
-      </c>
-      <c r="B23" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
-        <v>0.67000000000000015</v>
-      </c>
-      <c r="B24" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
-        <v>0.68000000000000016</v>
-      </c>
-      <c r="B25" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
-        <v>0.69000000000000017</v>
-      </c>
-      <c r="B26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
-        <v>0.70000000000000018</v>
-      </c>
-      <c r="B27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
-        <v>0.71000000000000019</v>
-      </c>
-      <c r="B28" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
-        <v>0.7200000000000002</v>
-      </c>
-      <c r="B29" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
-        <v>0.7300000000000002</v>
-      </c>
-      <c r="B30" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
-        <v>0.74000000000000021</v>
-      </c>
-      <c r="B31" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
-        <v>0.75000000000000022</v>
-      </c>
-      <c r="B32" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
-        <v>0.76000000000000023</v>
-      </c>
-      <c r="B33" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
-        <v>0.77000000000000024</v>
-      </c>
-      <c r="B34" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
-        <v>0.78000000000000025</v>
-      </c>
-      <c r="B35" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="16">
-        <v>0.79000000000000026</v>
-      </c>
-      <c r="B36" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="16">
-        <v>0.80000000000000027</v>
-      </c>
-      <c r="B37" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
-        <v>0.81000000000000028</v>
-      </c>
-      <c r="B38" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
-        <v>0.82000000000000028</v>
-      </c>
-      <c r="B39" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="16">
-        <v>0.83000000000000029</v>
-      </c>
-      <c r="B40" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="16">
-        <v>0.8400000000000003</v>
-      </c>
-      <c r="B41" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="16">
-        <v>0.85000000000000031</v>
-      </c>
-      <c r="B42" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="16">
-        <v>0.86000000000000032</v>
-      </c>
-      <c r="B43" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="16">
-        <v>0.87000000000000033</v>
-      </c>
-      <c r="B44" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="16">
-        <v>0.88000000000000034</v>
-      </c>
-      <c r="B45" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
-        <v>0.89000000000000035</v>
-      </c>
-      <c r="B46" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="16">
-        <v>0.90000000000000036</v>
-      </c>
-      <c r="B47" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="16">
-        <v>0.91000000000000036</v>
-      </c>
-      <c r="B48" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="16">
-        <v>0.92000000000000037</v>
-      </c>
-      <c r="B49" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="16">
-        <v>0.93000000000000038</v>
-      </c>
-      <c r="B50" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="16">
-        <v>0.94000000000000039</v>
-      </c>
-      <c r="B51" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="16">
-        <v>0.9500000000000004</v>
-      </c>
-      <c r="B52" s="17">
-        <v>0</v>
-      </c>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="27">
+        <v>0.39937236000501602</v>
+      </c>
+      <c r="B9" s="27">
+        <v>4.8785133091925901E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="27">
+        <v>0.451255237427102</v>
+      </c>
+      <c r="B10" s="27">
+        <v>4.54206345160201E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="27">
+        <v>0.499790758293094</v>
+      </c>
+      <c r="B11" s="27">
+        <v>4.0373918738397596E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>0.54999995743713403</v>
+      </c>
+      <c r="B12" s="27">
+        <v>3.8691637364208298E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="27">
+        <v>0.60020915658117302</v>
+      </c>
+      <c r="B13" s="27">
+        <v>1.2616815113045099E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="27">
+        <v>0.64958154850833905</v>
+      </c>
+      <c r="B14" s="27">
+        <v>2.6579442490947201E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="27">
+        <v>0.69979074765237803</v>
+      </c>
+      <c r="B15" s="27">
+        <v>4.3738321055594401E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="27">
+        <v>0.751673625074464</v>
+      </c>
+      <c r="B16" s="27">
+        <v>5.9551403398502803E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>0.800209145940457</v>
+      </c>
+      <c r="B17" s="27">
+        <v>7.1327103493442401E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="27">
+        <v>0.85041834508449698</v>
+      </c>
+      <c r="B18" s="27">
+        <v>7.8897196411617895E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
+        <v>0.90062754422853597</v>
+      </c>
+      <c r="B19" s="27">
+        <v>8.4953272992194795E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{2A74D785-ECF9-41EC-83E7-D06BFD039F5C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{617DEB09-F711-4141-A8DE-6968452326CC}">
       <formula1>"n-heptano, n-pentano"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E17C7ABB-BD74-4BD8-89A4-BE9C8A53E418}">
-  <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB55880-E0C2-438D-9EB5-ECC724CA1ECD}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -3447,55 +8200,56 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31.726299999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="5">
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27.2151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>34.716700000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="6">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6.3418999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="14">
-        <v>296.14999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <f>273.15+25</f>
+        <v>298.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -3503,430 +8257,891 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="16">
-        <v>0.44</v>
-      </c>
-      <c r="B9" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
-        <v>0.45</v>
-      </c>
-      <c r="B10" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
-        <v>0.46</v>
-      </c>
-      <c r="B11" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="B12" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
-        <v>0.48000000000000004</v>
-      </c>
-      <c r="B13" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
-        <v>0.49000000000000005</v>
-      </c>
-      <c r="B14" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="B15" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
-        <v>0.51</v>
-      </c>
-      <c r="B16" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
-        <v>0.52</v>
-      </c>
-      <c r="B17" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
-        <v>0.53</v>
-      </c>
-      <c r="B18" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
-        <v>0.54</v>
-      </c>
-      <c r="B19" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="B20" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B21" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="B22" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
-        <v>0.58000000000000007</v>
-      </c>
-      <c r="B23" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="B24" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="B25" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
-        <v>0.6100000000000001</v>
-      </c>
-      <c r="B26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
-        <v>0.62000000000000011</v>
-      </c>
-      <c r="B27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
-        <v>0.63000000000000012</v>
-      </c>
-      <c r="B28" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
-        <v>0.64000000000000012</v>
-      </c>
-      <c r="B29" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
-        <v>0.65000000000000013</v>
-      </c>
-      <c r="B30" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
-        <v>0.66000000000000014</v>
-      </c>
-      <c r="B31" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
-        <v>0.67000000000000015</v>
-      </c>
-      <c r="B32" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
-        <v>0.68000000000000016</v>
-      </c>
-      <c r="B33" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
-        <v>0.69000000000000017</v>
-      </c>
-      <c r="B34" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
-        <v>0.70000000000000018</v>
-      </c>
-      <c r="B35" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="16">
-        <v>0.71000000000000019</v>
-      </c>
-      <c r="B36" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="16">
-        <v>0.7200000000000002</v>
-      </c>
-      <c r="B37" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
-        <v>0.7300000000000002</v>
-      </c>
-      <c r="B38" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
-        <v>0.74000000000000021</v>
-      </c>
-      <c r="B39" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="16">
-        <v>0.75000000000000022</v>
-      </c>
-      <c r="B40" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="16">
-        <v>0.76000000000000023</v>
-      </c>
-      <c r="B41" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="16">
-        <v>0.77000000000000024</v>
-      </c>
-      <c r="B42" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="16">
-        <v>0.78000000000000025</v>
-      </c>
-      <c r="B43" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="16">
-        <v>0.79000000000000026</v>
-      </c>
-      <c r="B44" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="16">
-        <v>0.80000000000000027</v>
-      </c>
-      <c r="B45" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
-        <v>0.81000000000000028</v>
-      </c>
-      <c r="B46" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="16">
-        <v>0.82000000000000028</v>
-      </c>
-      <c r="B47" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="16">
-        <v>0.83000000000000029</v>
-      </c>
-      <c r="B48" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="16">
-        <v>0.8400000000000003</v>
-      </c>
-      <c r="B49" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="16">
-        <v>0.85000000000000031</v>
-      </c>
-      <c r="B50" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="16">
-        <v>0.86000000000000032</v>
-      </c>
-      <c r="B51" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="16">
-        <v>0.87000000000000033</v>
-      </c>
-      <c r="B52" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="16">
-        <v>0.88000000000000034</v>
-      </c>
-      <c r="B53" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="16">
-        <v>0.89000000000000035</v>
-      </c>
-      <c r="B54" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="16">
-        <v>0.90000000000000036</v>
-      </c>
-      <c r="B55" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="16">
-        <v>0.91000000000000036</v>
-      </c>
-      <c r="B56" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="16">
-        <v>0.92000000000000037</v>
-      </c>
-      <c r="B57" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="16">
-        <v>0.93000000000000038</v>
-      </c>
-      <c r="B58" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="16">
-        <v>0.94000000000000039</v>
-      </c>
-      <c r="B59" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="16">
-        <v>0.9500000000000004</v>
-      </c>
-      <c r="B60" s="17">
-        <v>0</v>
-      </c>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.400209231066188</v>
+      </c>
+      <c r="B9" s="19">
+        <v>1.8504710081246E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.45041843021022798</v>
+      </c>
+      <c r="B10" s="19">
+        <v>3.0280423010680198E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.499790758293094</v>
+      </c>
+      <c r="B11" s="19">
+        <v>2.85982058089635E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.54999995743713403</v>
+      </c>
+      <c r="B12" s="19">
+        <v>3.0280423010680198E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.60020915658117302</v>
+      </c>
+      <c r="B13" s="19">
+        <v>8.9158923485378096E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.65125522678638603</v>
+      </c>
+      <c r="B14" s="19">
+        <v>1.46355206758359E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
+        <v>0.69979074765237803</v>
+      </c>
+      <c r="B15" s="19">
+        <v>2.7252342206128401E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>0.74999994679641802</v>
+      </c>
+      <c r="B16" s="19">
+        <v>4.17196283272981E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19">
+        <v>0.80104595315733196</v>
+      </c>
+      <c r="B17" s="19">
+        <v>5.3327106702066099E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>0.85125515230137105</v>
+      </c>
+      <c r="B18" s="19">
+        <v>6.4093454015610299E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>0.90062754422853597</v>
+      </c>
+      <c r="B19" s="19">
+        <v>6.6448599810120704E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="25"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="25"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="25"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{9887C3D9-0565-4471-929F-C8627F7789A8}">
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{A4EBC5D0-72EF-42B6-A9B5-72A20F2F5D09}">
       <formula1>"n-heptano, n-pentano"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BC7EAE-C24A-4760-A622-67B9514C73F0}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>31.726299999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>27.2151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>34.716700000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>6.3418999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>273.15+50</f>
+        <v>323.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.400209231066188</v>
+      </c>
+      <c r="B9" s="19">
+        <v>2.3551490031341201E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.44958155914905501</v>
+      </c>
+      <c r="B10" s="19">
+        <v>1.1775777101906901E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.499790758293094</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1.5140275677812899E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.55251044293205498</v>
+      </c>
+      <c r="B12" s="19">
+        <v>1.8504710081246E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.59937234936429895</v>
+      </c>
+      <c r="B13" s="19">
+        <v>6.7289971518117104E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.65125522678638603</v>
+      </c>
+      <c r="B14" s="19">
+        <v>3.5327138788302402E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
+        <v>0.69979074765237803</v>
+      </c>
+      <c r="B15" s="19">
+        <v>1.5308413973769801E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>0.75083675401329197</v>
+      </c>
+      <c r="B16" s="19">
+        <v>3.02803780899491E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19">
+        <v>0.80188282421850399</v>
+      </c>
+      <c r="B17" s="19">
+        <v>3.6841127852600103E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>0.85041834508449698</v>
+      </c>
+      <c r="B18" s="19">
+        <v>4.6261685361652802E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>0.90062754422853597</v>
+      </c>
+      <c r="B19" s="19">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="25"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="25"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{9FDAB7E3-CBF3-4FFF-8B5C-EBB5A620F0D9}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F95BA82-F4F0-4154-A8A9-7E76B0212EB5}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>273.15+5</f>
+        <v>278.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.39957983839790401</v>
+      </c>
+      <c r="B9" s="19">
+        <v>4.7368280945150696E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.44999999999999901</v>
+      </c>
+      <c r="B10" s="19">
+        <v>4.2293234750652902E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.50042016160209501</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1.69172939002613E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.54999999999999905</v>
+      </c>
+      <c r="B12" s="19">
+        <v>4.3984938326937202E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.60042016160209499</v>
+      </c>
+      <c r="B13" s="19">
+        <v>1.64097763739404E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.64999999999999902</v>
+      </c>
+      <c r="B14" s="19">
+        <v>3.1296993715483098E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
+        <v>0.70042016160209497</v>
+      </c>
+      <c r="B15" s="19">
+        <v>4.0601505360626802E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>0.75084032320419103</v>
+      </c>
+      <c r="B16" s="19">
+        <v>5.1259399227104298E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19">
+        <v>0.80042009748954401</v>
+      </c>
+      <c r="B17" s="19">
+        <v>6.3439852125979398E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>0.84999993588744904</v>
+      </c>
+      <c r="B18" s="19">
+        <v>7.2575183733341403E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>0.90042009748954399</v>
+      </c>
+      <c r="B19" s="19">
+        <v>7.8327071080880994E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{6A64A87A-81F8-4E49-9696-22F54FDE89F1}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ABFCAE7-C90F-423F-9179-F612152B062D}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>273.15+25</f>
+        <v>298.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.40042016160209498</v>
+      </c>
+      <c r="B9" s="19">
+        <v>2.3684172739752798E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.45084032320419098</v>
+      </c>
+      <c r="B10" s="19">
+        <v>2.5375940850391899E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.49873951519371201</v>
+      </c>
+      <c r="B11" s="19">
+        <v>1.35336931446285E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.54999999999999905</v>
+      </c>
+      <c r="B12" s="19">
+        <v>2.8759412537315001E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.59957983839790396</v>
+      </c>
+      <c r="B13" s="19">
+        <v>8.9661515695803693E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.65084032320419105</v>
+      </c>
+      <c r="B14" s="19">
+        <v>2.0300752680313401E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
+        <v>0.69957977428535301</v>
+      </c>
+      <c r="B15" s="19">
+        <v>3.29887231055093E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>0.75084032320419103</v>
+      </c>
+      <c r="B16" s="19">
+        <v>4.5169176004384401E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19">
+        <v>0.80042009748954401</v>
+      </c>
+      <c r="B17" s="19">
+        <v>5.3796993312143403E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>0.84999993588744904</v>
+      </c>
+      <c r="B18" s="19">
+        <v>6.1748122735953301E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>0.90042009748954399</v>
+      </c>
+      <c r="B19" s="19">
+        <v>6.5469925457980097E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="25"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="25"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{534464F6-E810-446F-B613-082EDBB56AF0}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B759301-59AD-457A-9C30-ABE010111AF9}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>273.15+50</f>
+        <v>323.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>0.40042016160209498</v>
+      </c>
+      <c r="B9" s="19">
+        <v>5.4135353387706701E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>0.44999999999999901</v>
+      </c>
+      <c r="B10" s="19">
+        <v>4.3984938326937202E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>0.50042016160209501</v>
+      </c>
+      <c r="B11" s="19">
+        <v>4.7368280945150696E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>0.54999999999999905</v>
+      </c>
+      <c r="B12" s="19">
+        <v>1.8608997476545399E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>0.60042016160209499</v>
+      </c>
+      <c r="B13" s="19">
+        <v>3.0450987044889498E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="19">
+        <v>0.65084032320419105</v>
+      </c>
+      <c r="B14" s="19">
+        <v>9.8120162645934407E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
+        <v>0.70042016160209497</v>
+      </c>
+      <c r="B15" s="19">
+        <v>2.3853381817993999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="19">
+        <v>0.74999993588744895</v>
+      </c>
+      <c r="B16" s="19">
+        <v>3.40037581581508E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19">
+        <v>0.80042009748954401</v>
+      </c>
+      <c r="B17" s="19">
+        <v>4.5169176004384401E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
+        <v>0.85084025909163996</v>
+      </c>
+      <c r="B18" s="19">
+        <v>4.5169176004384401E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="19">
+        <v>0.90042009748954399</v>
+      </c>
+      <c r="B19" s="19">
+        <v>5.5827069870861903E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D20" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="25"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" s="25"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D20:H20"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{B2B55D59-213F-4EA9-A284-0DB001AA1C8D}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
+++ b/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor\OneDrive\Documentos\Vitor\Projetos\PycharmProjects\Projeto_TotalEnergies\Código_Pré_Modificações_Fred\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5FFA92-C2DC-4444-B0F5-7874CA72DC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC30955E-0E3E-4FEE-B21E-BE89E0251DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Yanes_P1" sheetId="4" r:id="rId1"/>
@@ -25,8 +25,9 @@
     <sheet name="Alves_BR3_5C" sheetId="16" r:id="rId10"/>
     <sheet name="Alves_BR3_25C" sheetId="17" r:id="rId11"/>
     <sheet name="Alves_BR3_50C" sheetId="18" r:id="rId12"/>
-    <sheet name="Tharanivasan_Lloydminster_1" sheetId="8" r:id="rId13"/>
-    <sheet name="Tharanivasan_Lloydminster_2" sheetId="9" r:id="rId14"/>
+    <sheet name="Tharanivasan_Lloydminster_hept" sheetId="8" r:id="rId13"/>
+    <sheet name="Tharanivasan_Lloydminster_pent" sheetId="9" r:id="rId14"/>
+    <sheet name="Tharanivasan_Lloydminster_heptM" sheetId="20" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="13">
   <si>
     <t>Saturados</t>
   </si>
@@ -94,11 +95,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.000000000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -285,7 +287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -362,10 +364,13 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2665,6 +2670,448 @@
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                 <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA3EA911-3789-42A7-568B-623D99FB5877}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8991600" y="161925"/>
+            <a:ext cx="6658904" cy="3334215"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>86654</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Agrupar 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C10AC3F-B1BF-4859-8990-4072DF2DCCB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2244089" y="85725"/>
+          <a:ext cx="13402605" cy="5029200"/>
+          <a:chOff x="2247899" y="161925"/>
+          <a:chExt cx="13402605" cy="5238750"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="3" name="Agrupar 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63B31CE4-67CF-C999-3B90-9D412EB91180}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="2247899" y="180975"/>
+            <a:ext cx="6562726" cy="2771775"/>
+            <a:chOff x="2247899" y="180975"/>
+            <a:chExt cx="6562726" cy="2781300"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="6" name="Imagem 5">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A9D735A-D168-1177-1659-D6D0FCECF3C5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2257424" y="180975"/>
+              <a:ext cx="6477904" cy="2086266"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="7" name="CaixaDeTexto 6">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE5D2B50-D126-7B99-2D63-9ACD1C9F81C2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2247899" y="2343150"/>
+              <a:ext cx="6562726" cy="619125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="12700" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1600"/>
+                <a:t>Dados de yields não disponíveis na tese</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1600" baseline="0"/>
+                <a:t> nem</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1600"/>
+                <a:t> no artigo de Akbarzadeh (2005 )</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="CaixaDeTexto 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B849BE8-AEF1-1C25-3AE1-6E202F98E869}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="9134924" y="3590925"/>
+            <a:ext cx="6352725" cy="1809750"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="38100" cmpd="sng">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400"/>
+              <a:t>As variáveis destacadas acima alimentam</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0"/>
+              <a:t> o</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400"/>
+              <a:t> arquivo</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0"/>
+              <a:t>: </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>'variáveis_entrada_código.txt'</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1400"/>
+          </a:p>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400"/>
+              <a:t>n_agregados = 30</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400"/>
+              <a:t>MWmin</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0"/>
+              <a:t> = 1800</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0"/>
+              <a:t>MWmax = 30000</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0"/>
+              <a:t>alfa = 3.5 (Obs: embora o Tharanivasan chame </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>de </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1400" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>β</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>, no nosso código o fator de forma da distribuição Gamma é a variável 'alfa'.)</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>MWavg = 3620.</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1400">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="5" name="Imagem 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{816FA57E-8AD0-F35D-5399-72836AF2C650}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -6405,13 +6852,13 @@
       <c r="B19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="25"/>
@@ -6572,13 +7019,13 @@
       <c r="B19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6716,13 +7163,13 @@
       </c>
     </row>
     <row r="20" spans="4:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="25"/>
@@ -6743,7 +7190,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D94E3C-228A-404B-AAAA-84368A7243B9}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
@@ -6815,358 +7262,216 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
-        <v>0.52</v>
-      </c>
-      <c r="B9" s="17">
-        <v>0</v>
+      <c r="A9" s="27">
+        <v>0.50725668750098696</v>
+      </c>
+      <c r="B9" s="27">
+        <v>3.2786886612808999E-3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
-        <v>0.53</v>
-      </c>
-      <c r="B10" s="17">
-        <v>0</v>
+      <c r="A10" s="27">
+        <v>0.53805307870333796</v>
+      </c>
+      <c r="B10" s="27">
+        <v>5.2458968551676198E-3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
-        <v>0.54</v>
-      </c>
-      <c r="B11" s="17">
-        <v>0</v>
+      <c r="A11" s="27">
+        <v>0.57840708796312601</v>
+      </c>
+      <c r="B11" s="27">
+        <v>2.2622919244106199E-2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="16">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="B12" s="17">
-        <v>0</v>
+      <c r="A12" s="27">
+        <v>0.67185843518573596</v>
+      </c>
+      <c r="B12" s="27">
+        <v>6.7868845282751306E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="16">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B13" s="17">
-        <v>0</v>
+      <c r="A13" s="27">
+        <v>0.70371683796342999</v>
+      </c>
+      <c r="B13" s="27">
+        <v>8.0655736064628794E-2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="B14" s="17">
-        <v>0</v>
+      <c r="A14" s="27">
+        <v>0.73345129861054503</v>
+      </c>
+      <c r="B14" s="27">
+        <v>9.4426230943449693E-2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
-        <v>0.58000000000000007</v>
-      </c>
-      <c r="B15" s="17">
-        <v>0</v>
+      <c r="A15" s="27">
+        <v>0.77380530787033297</v>
+      </c>
+      <c r="B15" s="27">
+        <v>0.10163933599250401</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="B16" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="16">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="B17" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="16">
-        <v>0.6100000000000001</v>
-      </c>
-      <c r="B18" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="16">
-        <v>0.62000000000000011</v>
-      </c>
-      <c r="B19" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
-        <v>0.63000000000000012</v>
-      </c>
-      <c r="B20" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
-        <v>0.64000000000000012</v>
-      </c>
-      <c r="B21" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="16">
-        <v>0.65000000000000013</v>
-      </c>
-      <c r="B22" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
-        <v>0.66000000000000014</v>
-      </c>
-      <c r="B23" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
-        <v>0.67000000000000015</v>
-      </c>
-      <c r="B24" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="16">
-        <v>0.68000000000000016</v>
-      </c>
-      <c r="B25" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="16">
-        <v>0.69000000000000017</v>
-      </c>
-      <c r="B26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="16">
-        <v>0.70000000000000018</v>
-      </c>
-      <c r="B27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
-        <v>0.71000000000000019</v>
-      </c>
-      <c r="B28" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
-        <v>0.7200000000000002</v>
-      </c>
-      <c r="B29" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="16">
-        <v>0.7300000000000002</v>
-      </c>
-      <c r="B30" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
-        <v>0.74000000000000021</v>
-      </c>
-      <c r="B31" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="16">
-        <v>0.75000000000000022</v>
-      </c>
-      <c r="B32" s="17">
-        <v>0</v>
-      </c>
+      <c r="A16" s="27">
+        <v>0.87256630786911804</v>
+      </c>
+      <c r="B16" s="27">
+        <v>0.12327868866128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>0.93203539120356504</v>
+      </c>
+      <c r="B17" s="27">
+        <v>0.123606558778129</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="27">
+        <v>0.95433625694392898</v>
+      </c>
+      <c r="B18" s="27">
+        <v>0.129508183359789</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="16"/>
+      <c r="B24" s="17"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="16"/>
+      <c r="B26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="17"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="16"/>
+      <c r="B30" s="17"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="16"/>
+      <c r="B32" s="17"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="16">
-        <v>0.76000000000000023</v>
-      </c>
-      <c r="B33" s="17">
-        <v>0</v>
-      </c>
+      <c r="A33" s="16"/>
+      <c r="B33" s="17"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="16">
-        <v>0.77000000000000024</v>
-      </c>
-      <c r="B34" s="17">
-        <v>0</v>
-      </c>
+      <c r="A34" s="16"/>
+      <c r="B34" s="17"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="16">
-        <v>0.78000000000000025</v>
-      </c>
-      <c r="B35" s="17">
-        <v>0</v>
-      </c>
+      <c r="A35" s="16"/>
+      <c r="B35" s="17"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="16">
-        <v>0.79000000000000026</v>
-      </c>
-      <c r="B36" s="17">
-        <v>0</v>
-      </c>
+      <c r="A36" s="16"/>
+      <c r="B36" s="17"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="16">
-        <v>0.80000000000000027</v>
-      </c>
-      <c r="B37" s="17">
-        <v>0</v>
-      </c>
+      <c r="A37" s="16"/>
+      <c r="B37" s="17"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="16">
-        <v>0.81000000000000028</v>
-      </c>
-      <c r="B38" s="17">
-        <v>0</v>
-      </c>
+      <c r="A38" s="16"/>
+      <c r="B38" s="17"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="16">
-        <v>0.82000000000000028</v>
-      </c>
-      <c r="B39" s="17">
-        <v>0</v>
-      </c>
+      <c r="A39" s="16"/>
+      <c r="B39" s="17"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="16">
-        <v>0.83000000000000029</v>
-      </c>
-      <c r="B40" s="17">
-        <v>0</v>
-      </c>
+      <c r="A40" s="16"/>
+      <c r="B40" s="17"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="16">
-        <v>0.8400000000000003</v>
-      </c>
-      <c r="B41" s="17">
-        <v>0</v>
-      </c>
+      <c r="A41" s="16"/>
+      <c r="B41" s="17"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="16">
-        <v>0.85000000000000031</v>
-      </c>
-      <c r="B42" s="17">
-        <v>0</v>
-      </c>
+      <c r="A42" s="16"/>
+      <c r="B42" s="17"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="16">
-        <v>0.86000000000000032</v>
-      </c>
-      <c r="B43" s="17">
-        <v>0</v>
-      </c>
+      <c r="A43" s="16"/>
+      <c r="B43" s="17"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="16">
-        <v>0.87000000000000033</v>
-      </c>
-      <c r="B44" s="17">
-        <v>0</v>
-      </c>
+      <c r="A44" s="16"/>
+      <c r="B44" s="17"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="16">
-        <v>0.88000000000000034</v>
-      </c>
-      <c r="B45" s="17">
-        <v>0</v>
-      </c>
+      <c r="A45" s="16"/>
+      <c r="B45" s="17"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="16">
-        <v>0.89000000000000035</v>
-      </c>
-      <c r="B46" s="17">
-        <v>0</v>
-      </c>
+      <c r="A46" s="16"/>
+      <c r="B46" s="17"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="16">
-        <v>0.90000000000000036</v>
-      </c>
-      <c r="B47" s="17">
-        <v>0</v>
-      </c>
+      <c r="A47" s="16"/>
+      <c r="B47" s="17"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="16">
-        <v>0.91000000000000036</v>
-      </c>
-      <c r="B48" s="17">
-        <v>0</v>
-      </c>
+      <c r="A48" s="16"/>
+      <c r="B48" s="17"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="16">
-        <v>0.92000000000000037</v>
-      </c>
-      <c r="B49" s="17">
-        <v>0</v>
-      </c>
+      <c r="A49" s="16"/>
+      <c r="B49" s="17"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="16">
-        <v>0.93000000000000038</v>
-      </c>
-      <c r="B50" s="17">
-        <v>0</v>
-      </c>
+      <c r="A50" s="16"/>
+      <c r="B50" s="17"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="16">
-        <v>0.94000000000000039</v>
-      </c>
-      <c r="B51" s="17">
-        <v>0</v>
-      </c>
+      <c r="A51" s="16"/>
+      <c r="B51" s="17"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="16">
-        <v>0.9500000000000004</v>
-      </c>
-      <c r="B52" s="17">
-        <v>0</v>
-      </c>
+      <c r="A52" s="16"/>
+      <c r="B52" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D17:H17"/>
+  </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{2A74D785-ECF9-41EC-83E7-D06BFD039F5C}">
       <formula1>"n-heptano, n-pentano"</formula1>
@@ -7180,7 +7485,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E17C7ABB-BD74-4BD8-89A4-BE9C8A53E418}">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
@@ -7251,422 +7556,268 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
-        <v>0.44</v>
-      </c>
-      <c r="B9" s="17">
-        <v>0</v>
+      <c r="A9" s="27">
+        <v>0.44778760416654001</v>
+      </c>
+      <c r="B9" s="27">
+        <v>9.8360534766381204E-3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="16">
-        <v>0.45</v>
-      </c>
-      <c r="B10" s="17">
-        <v>0</v>
+      <c r="A10" s="27">
+        <v>0.48389381018527999</v>
+      </c>
+      <c r="B10" s="27">
+        <v>3.77049070975259E-2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="16">
-        <v>0.46</v>
-      </c>
-      <c r="B11" s="17">
-        <v>0</v>
+      <c r="A11" s="27">
+        <v>0.51469028240773895</v>
+      </c>
+      <c r="B11" s="27">
+        <v>7.0819670080786101E-2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="16">
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="B12" s="17">
-        <v>0</v>
+      <c r="A12" s="27">
+        <v>0.555044291667527</v>
+      </c>
+      <c r="B12" s="27">
+        <v>9.77049196047306E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="16">
-        <v>0.48000000000000004</v>
-      </c>
-      <c r="B13" s="17">
-        <v>0</v>
+      <c r="A13" s="27">
+        <v>0.65061950000060698</v>
+      </c>
+      <c r="B13" s="27">
+        <v>0.14196721027841999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
-        <v>0.49000000000000005</v>
-      </c>
-      <c r="B14" s="17">
-        <v>0</v>
+      <c r="A14" s="27">
+        <v>0.68460176388877003</v>
+      </c>
+      <c r="B14" s="27">
+        <v>0.15311475047605499</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="B15" s="17">
-        <v>0</v>
+      <c r="A15" s="27">
+        <v>0.71327429398065101</v>
+      </c>
+      <c r="B15" s="27">
+        <v>0.15442623094344901</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="16">
-        <v>0.51</v>
-      </c>
-      <c r="B16" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="16">
-        <v>0.52</v>
-      </c>
-      <c r="B17" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="16">
-        <v>0.53</v>
-      </c>
-      <c r="B18" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="16">
-        <v>0.54</v>
-      </c>
-      <c r="B19" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="B20" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="B21" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="16">
-        <v>0.57000000000000006</v>
-      </c>
-      <c r="B22" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="16">
-        <v>0.58000000000000007</v>
-      </c>
-      <c r="B23" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="16">
-        <v>0.59000000000000008</v>
-      </c>
-      <c r="B24" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="16">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="B25" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="16">
-        <v>0.6100000000000001</v>
-      </c>
-      <c r="B26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="16">
-        <v>0.62000000000000011</v>
-      </c>
-      <c r="B27" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="16">
-        <v>0.63000000000000012</v>
-      </c>
-      <c r="B28" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="16">
-        <v>0.64000000000000012</v>
-      </c>
-      <c r="B29" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="16">
-        <v>0.65000000000000013</v>
-      </c>
-      <c r="B30" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="16">
-        <v>0.66000000000000014</v>
-      </c>
-      <c r="B31" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="16">
-        <v>0.67000000000000015</v>
-      </c>
-      <c r="B32" s="17">
-        <v>0</v>
-      </c>
+      <c r="A16" s="27">
+        <v>0.75575216435090897</v>
+      </c>
+      <c r="B16" s="27">
+        <v>0.15999999791546499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>0.86088490972131904</v>
+      </c>
+      <c r="B17" s="27">
+        <v>0.15704917937103299</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="27">
+        <v>0.92460171527670498</v>
+      </c>
+      <c r="B18" s="27">
+        <v>0.15999999791546499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
+        <v>0.94796459259241195</v>
+      </c>
+      <c r="B19" s="27">
+        <v>0.154754094806695</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="16"/>
+      <c r="B21" s="17"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="16"/>
+      <c r="B22" s="17"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="16"/>
+      <c r="B24" s="17"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="16"/>
+      <c r="B26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="16"/>
+      <c r="B28" s="17"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="17"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="16"/>
+      <c r="B30" s="17"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="16"/>
+      <c r="B31" s="17"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="16"/>
+      <c r="B32" s="17"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="16">
-        <v>0.68000000000000016</v>
-      </c>
-      <c r="B33" s="17">
-        <v>0</v>
-      </c>
+      <c r="A33" s="16"/>
+      <c r="B33" s="17"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="16">
-        <v>0.69000000000000017</v>
-      </c>
-      <c r="B34" s="17">
-        <v>0</v>
-      </c>
+      <c r="A34" s="16"/>
+      <c r="B34" s="17"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="16">
-        <v>0.70000000000000018</v>
-      </c>
-      <c r="B35" s="17">
-        <v>0</v>
-      </c>
+      <c r="A35" s="16"/>
+      <c r="B35" s="17"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="16">
-        <v>0.71000000000000019</v>
-      </c>
-      <c r="B36" s="17">
-        <v>0</v>
-      </c>
+      <c r="A36" s="16"/>
+      <c r="B36" s="17"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="16">
-        <v>0.7200000000000002</v>
-      </c>
-      <c r="B37" s="17">
-        <v>0</v>
-      </c>
+      <c r="A37" s="16"/>
+      <c r="B37" s="17"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="16">
-        <v>0.7300000000000002</v>
-      </c>
-      <c r="B38" s="17">
-        <v>0</v>
-      </c>
+      <c r="A38" s="16"/>
+      <c r="B38" s="17"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="16">
-        <v>0.74000000000000021</v>
-      </c>
-      <c r="B39" s="17">
-        <v>0</v>
-      </c>
+      <c r="A39" s="16"/>
+      <c r="B39" s="17"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="16">
-        <v>0.75000000000000022</v>
-      </c>
-      <c r="B40" s="17">
-        <v>0</v>
-      </c>
+      <c r="A40" s="16"/>
+      <c r="B40" s="17"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="16">
-        <v>0.76000000000000023</v>
-      </c>
-      <c r="B41" s="17">
-        <v>0</v>
-      </c>
+      <c r="A41" s="16"/>
+      <c r="B41" s="17"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="16">
-        <v>0.77000000000000024</v>
-      </c>
-      <c r="B42" s="17">
-        <v>0</v>
-      </c>
+      <c r="A42" s="16"/>
+      <c r="B42" s="17"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="16">
-        <v>0.78000000000000025</v>
-      </c>
-      <c r="B43" s="17">
-        <v>0</v>
-      </c>
+      <c r="A43" s="16"/>
+      <c r="B43" s="17"/>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="16">
-        <v>0.79000000000000026</v>
-      </c>
-      <c r="B44" s="17">
-        <v>0</v>
-      </c>
+      <c r="A44" s="16"/>
+      <c r="B44" s="17"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="16">
-        <v>0.80000000000000027</v>
-      </c>
-      <c r="B45" s="17">
-        <v>0</v>
-      </c>
+      <c r="A45" s="16"/>
+      <c r="B45" s="17"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="16">
-        <v>0.81000000000000028</v>
-      </c>
-      <c r="B46" s="17">
-        <v>0</v>
-      </c>
+      <c r="A46" s="16"/>
+      <c r="B46" s="17"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="16">
-        <v>0.82000000000000028</v>
-      </c>
-      <c r="B47" s="17">
-        <v>0</v>
-      </c>
+      <c r="A47" s="16"/>
+      <c r="B47" s="17"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="16">
-        <v>0.83000000000000029</v>
-      </c>
-      <c r="B48" s="17">
-        <v>0</v>
-      </c>
+      <c r="A48" s="16"/>
+      <c r="B48" s="17"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="16">
-        <v>0.8400000000000003</v>
-      </c>
-      <c r="B49" s="17">
-        <v>0</v>
-      </c>
+      <c r="A49" s="16"/>
+      <c r="B49" s="17"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="16">
-        <v>0.85000000000000031</v>
-      </c>
-      <c r="B50" s="17">
-        <v>0</v>
-      </c>
+      <c r="A50" s="16"/>
+      <c r="B50" s="17"/>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="16">
-        <v>0.86000000000000032</v>
-      </c>
-      <c r="B51" s="17">
-        <v>0</v>
-      </c>
+      <c r="A51" s="16"/>
+      <c r="B51" s="17"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="16">
-        <v>0.87000000000000033</v>
-      </c>
-      <c r="B52" s="17">
-        <v>0</v>
-      </c>
+      <c r="A52" s="16"/>
+      <c r="B52" s="17"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="16">
-        <v>0.88000000000000034</v>
-      </c>
-      <c r="B53" s="17">
-        <v>0</v>
-      </c>
+      <c r="A53" s="16"/>
+      <c r="B53" s="17"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="16">
-        <v>0.89000000000000035</v>
-      </c>
-      <c r="B54" s="17">
-        <v>0</v>
-      </c>
+      <c r="A54" s="16"/>
+      <c r="B54" s="17"/>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="16">
-        <v>0.90000000000000036</v>
-      </c>
-      <c r="B55" s="17">
-        <v>0</v>
-      </c>
+      <c r="A55" s="16"/>
+      <c r="B55" s="17"/>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="16">
-        <v>0.91000000000000036</v>
-      </c>
-      <c r="B56" s="17">
-        <v>0</v>
-      </c>
+      <c r="A56" s="16"/>
+      <c r="B56" s="17"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="16">
-        <v>0.92000000000000037</v>
-      </c>
-      <c r="B57" s="17">
-        <v>0</v>
-      </c>
+      <c r="A57" s="16"/>
+      <c r="B57" s="17"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="16">
-        <v>0.93000000000000038</v>
-      </c>
-      <c r="B58" s="17">
-        <v>0</v>
-      </c>
+      <c r="A58" s="16"/>
+      <c r="B58" s="17"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="16">
-        <v>0.94000000000000039</v>
-      </c>
-      <c r="B59" s="17">
-        <v>0</v>
-      </c>
+      <c r="A59" s="16"/>
+      <c r="B59" s="17"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="16">
-        <v>0.9500000000000004</v>
-      </c>
-      <c r="B60" s="17">
-        <v>0</v>
-      </c>
+      <c r="A60" s="16"/>
+      <c r="B60" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D17:H17"/>
+  </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{9887C3D9-0565-4471-929F-C8627F7789A8}">
       <formula1>"n-heptano, n-pentano"</formula1>
@@ -7675,6 +7826,408 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF99C0D-B9B7-4851-BE57-EA3A1C500665}">
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.6640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="14">
+        <f>23+273.15</f>
+        <v>296.14999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="27">
+        <v>0.50725668750098696</v>
+      </c>
+      <c r="B9" s="27">
+        <v>6.5573773225618198E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="27">
+        <v>0.52106194675925599</v>
+      </c>
+      <c r="B10" s="27">
+        <v>7.5409689123005002E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="27">
+        <v>0.536991148148103</v>
+      </c>
+      <c r="B11" s="27">
+        <v>9.8360534766381204E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>0.55398228009218398</v>
+      </c>
+      <c r="B12" s="27">
+        <v>1.3114742137919E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="27">
+        <v>0.56778762037056096</v>
+      </c>
+      <c r="B13" s="27">
+        <v>1.6393430799199901E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="27">
+        <v>0.58159296064893795</v>
+      </c>
+      <c r="B14" s="27">
+        <v>1.9999995830931701E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="27">
+        <v>0.59433628935197202</v>
+      </c>
+      <c r="B15" s="27">
+        <v>2.42622635747466E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="27">
+        <v>0.60495575694453696</v>
+      </c>
+      <c r="B16" s="27">
+        <v>2.8524581347380201E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>0.61769908564757103</v>
+      </c>
+      <c r="B17" s="27">
+        <v>3.37704907097525E-2</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="27">
+        <v>0.62725662268490101</v>
+      </c>
+      <c r="B18" s="27">
+        <v>3.8032783467976797E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
+        <v>0.641061962963278</v>
+      </c>
+      <c r="B19" s="27">
+        <v>4.4262284420087797E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="27">
+        <v>0.652743361111077</v>
+      </c>
+      <c r="B20" s="27">
+        <v>5.0163921508952498E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="27">
+        <v>0.66442475925887601</v>
+      </c>
+      <c r="B21" s="27">
+        <v>5.5409805856915399E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="27">
+        <v>0.67292036574097103</v>
+      </c>
+      <c r="B22" s="27">
+        <v>6.0327863863246199E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="27">
+        <v>0.68566369444400499</v>
+      </c>
+      <c r="B23" s="27">
+        <v>6.6229500952110901E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="27">
+        <v>0.69840710416714702</v>
+      </c>
+      <c r="B24" s="27">
+        <v>7.1803274177729401E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="27">
+        <v>0.71008850231494602</v>
+      </c>
+      <c r="B25" s="27">
+        <v>7.8032787637045006E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="27">
+        <v>0.72070796990751096</v>
+      </c>
+      <c r="B26" s="27">
+        <v>8.2950820628966401E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="27">
+        <v>0.73132743750007501</v>
+      </c>
+      <c r="B27" s="27">
+        <v>8.7540977250436899E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="27">
+        <v>0.74194690509264005</v>
+      </c>
+      <c r="B28" s="27">
+        <v>9.1803270008661203E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="27">
+        <v>0.75362830324043895</v>
+      </c>
+      <c r="B29" s="27">
+        <v>9.6393439137336306E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="27">
+        <v>0.76743364351881604</v>
+      </c>
+      <c r="B30" s="27">
+        <v>0.100327868032314</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="27">
+        <v>0.775929168980803</v>
+      </c>
+      <c r="B31" s="27">
+        <v>0.103606556693595</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="27">
+        <v>0.79079643981441505</v>
+      </c>
+      <c r="B32" s="27">
+        <v>0.108196713315065</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="27">
+        <v>0.805663710648027</v>
+      </c>
+      <c r="B33" s="27">
+        <v>0.112131142210043</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="27">
+        <v>0.82265484259210797</v>
+      </c>
+      <c r="B34" s="27">
+        <v>0.115737700988173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="27">
+        <v>0.83964597453619005</v>
+      </c>
+      <c r="B35" s="27">
+        <v>0.119344259766302</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="27">
+        <v>0.85982297916608397</v>
+      </c>
+      <c r="B36" s="27">
+        <v>0.12229507831073499</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <v>0.87893805324074303</v>
+      </c>
+      <c r="B37" s="27">
+        <v>0.124918032991921</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="27">
+        <v>0.90017698842587202</v>
+      </c>
+      <c r="B38" s="27">
+        <v>0.12590163708886401</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="27">
+        <v>0.91823005092518795</v>
+      </c>
+      <c r="B39" s="27">
+        <v>0.12688524743940999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <v>0.93522118286927003</v>
+      </c>
+      <c r="B40" s="27">
+        <v>0.126557377322561</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <v>0.95115038425811704</v>
+      </c>
+      <c r="B41" s="27">
+        <v>0.124918032991921</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="16"/>
+      <c r="B42" s="17"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="16"/>
+      <c r="B43" s="17"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="16"/>
+      <c r="B44" s="17"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="16"/>
+      <c r="B45" s="17"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="16"/>
+      <c r="B46" s="17"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="16"/>
+      <c r="B47" s="17"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="16"/>
+      <c r="B48" s="17"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="16"/>
+      <c r="B49" s="17"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="16"/>
+      <c r="B50" s="17"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="16"/>
+      <c r="B51" s="17"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="16"/>
+      <c r="B52" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D17:H17"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7" xr:uid="{8310692E-EC9A-4885-85E2-F4369B6C60C1}">
+      <formula1>"n-heptano, n-pentano"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7977,13 +8530,13 @@
       <c r="B18" s="22">
         <v>1.0418602841124299E-2</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8074,101 +8627,101 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="27">
+      <c r="A9" s="26">
         <v>0.39937236000501602</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="26">
         <v>4.8785133091925901E-3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="27">
+      <c r="A10" s="26">
         <v>0.451255237427102</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>4.54206345160201E-3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="27">
+      <c r="A11" s="26">
         <v>0.499790758293094</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="26">
         <v>4.0373918738397596E-3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="27">
+      <c r="A12" s="26">
         <v>0.54999995743713403</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>3.8691637364208298E-3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="27">
+      <c r="A13" s="26">
         <v>0.60020915658117302</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>1.2616815113045099E-2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="27">
+      <c r="A14" s="26">
         <v>0.64958154850833905</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="26">
         <v>2.6579442490947201E-2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="27">
+      <c r="A15" s="26">
         <v>0.69979074765237803</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>4.3738321055594401E-2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="27">
+      <c r="A16" s="26">
         <v>0.751673625074464</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>5.9551403398502803E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="27">
+      <c r="A17" s="26">
         <v>0.800209145940457</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>7.1327103493442401E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="27">
+      <c r="A18" s="26">
         <v>0.85041834508449698</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>7.8897196411617895E-2</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="27">
+      <c r="A19" s="26">
         <v>0.90062754422853597</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>8.4953272992194795E-2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8346,13 +8899,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B32" s="25"/>
@@ -8542,13 +9095,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="25"/>
@@ -8735,13 +9288,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="25"/>
@@ -8922,13 +9475,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="25"/>
@@ -9115,13 +9668,13 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="25"/>

--- a/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
+++ b/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor\OneDrive\Documentos\Vitor\Projetos\PycharmProjects\Projeto_TotalEnergies\Código_Pré_Modificações_Fred\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC30955E-0E3E-4FEE-B21E-BE89E0251DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748D41C7-8D0E-4254-8E5E-E53BD16D43BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Yanes_P1" sheetId="4" r:id="rId1"/>
@@ -7263,74 +7263,74 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
-        <v>0.50725668750098696</v>
+        <v>0</v>
       </c>
       <c r="B9" s="27">
-        <v>3.2786886612808999E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
-        <v>0.53805307870333796</v>
+        <v>0.50725668750098696</v>
       </c>
       <c r="B10" s="27">
-        <v>5.2458968551676198E-3</v>
+        <v>3.2786886612808999E-3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="27">
-        <v>0.57840708796312601</v>
+        <v>0.53805307870333796</v>
       </c>
       <c r="B11" s="27">
-        <v>2.2622919244106199E-2</v>
+        <v>5.2458968551676198E-3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="27">
-        <v>0.67185843518573596</v>
+        <v>0.57840708796312601</v>
       </c>
       <c r="B12" s="27">
-        <v>6.7868845282751306E-2</v>
+        <v>2.2622919244106199E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="27">
-        <v>0.70371683796342999</v>
+        <v>0.67185843518573596</v>
       </c>
       <c r="B13" s="27">
-        <v>8.0655736064628794E-2</v>
+        <v>6.7868845282751306E-2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
-        <v>0.73345129861054503</v>
+        <v>0.70371683796342999</v>
       </c>
       <c r="B14" s="27">
-        <v>9.4426230943449693E-2</v>
+        <v>8.0655736064628794E-2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="27">
-        <v>0.77380530787033297</v>
+        <v>0.73345129861054503</v>
       </c>
       <c r="B15" s="27">
-        <v>0.10163933599250401</v>
+        <v>9.4426230943449693E-2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
-        <v>0.87256630786911804</v>
+        <v>0.77380530787033297</v>
       </c>
       <c r="B16" s="27">
-        <v>0.12327868866128</v>
+        <v>0.10163933599250401</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
-        <v>0.93203539120356504</v>
+        <v>0.87256630786911804</v>
       </c>
       <c r="B17" s="27">
-        <v>0.123606558778129</v>
+        <v>0.12327868866128</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>12</v>
@@ -7342,9 +7342,17 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
+        <v>0.93203539120356504</v>
+      </c>
+      <c r="B18" s="27">
+        <v>0.123606558778129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
         <v>0.95433625694392898</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B19" s="27">
         <v>0.129508183359789</v>
       </c>
     </row>

--- a/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
+++ b/Código_Pré_Modificações_Fred/dados_experimentais.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitor\OneDrive\Documentos\Vitor\Projetos\PycharmProjects\Projeto_TotalEnergies\Código_Pré_Modificações_Fred\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748D41C7-8D0E-4254-8E5E-E53BD16D43BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C3D30D-74E7-4F1D-B2A3-25AE489289EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Yanes_P1" sheetId="4" r:id="rId1"/>
@@ -7263,74 +7263,74 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
-        <v>0</v>
+        <v>0.50725668750098696</v>
       </c>
       <c r="B9" s="27">
-        <v>0</v>
+        <v>3.2786886612808999E-3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
-        <v>0.50725668750098696</v>
+        <v>0.53805307870333796</v>
       </c>
       <c r="B10" s="27">
-        <v>3.2786886612808999E-3</v>
+        <v>5.2458968551676198E-3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="27">
-        <v>0.53805307870333796</v>
+        <v>0.57840708796312601</v>
       </c>
       <c r="B11" s="27">
-        <v>5.2458968551676198E-3</v>
+        <v>2.2622919244106199E-2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="27">
-        <v>0.57840708796312601</v>
+        <v>0.67185843518573596</v>
       </c>
       <c r="B12" s="27">
-        <v>2.2622919244106199E-2</v>
+        <v>6.7868845282751306E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="27">
-        <v>0.67185843518573596</v>
+        <v>0.70371683796342999</v>
       </c>
       <c r="B13" s="27">
-        <v>6.7868845282751306E-2</v>
+        <v>8.0655736064628794E-2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
-        <v>0.70371683796342999</v>
+        <v>0.73345129861054503</v>
       </c>
       <c r="B14" s="27">
-        <v>8.0655736064628794E-2</v>
+        <v>9.4426230943449693E-2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="27">
-        <v>0.73345129861054503</v>
+        <v>0.77380530787033297</v>
       </c>
       <c r="B15" s="27">
-        <v>9.4426230943449693E-2</v>
+        <v>0.10163933599250401</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
-        <v>0.77380530787033297</v>
+        <v>0.87256630786911804</v>
       </c>
       <c r="B16" s="27">
-        <v>0.10163933599250401</v>
+        <v>0.12327868866128</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
-        <v>0.87256630786911804</v>
+        <v>0.93203539120356504</v>
       </c>
       <c r="B17" s="27">
-        <v>0.12327868866128</v>
+        <v>0.123606558778129</v>
       </c>
       <c r="D17" s="28" t="s">
         <v>12</v>
@@ -7342,17 +7342,9 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
-        <v>0.93203539120356504</v>
+        <v>0.95433625694392898</v>
       </c>
       <c r="B18" s="27">
-        <v>0.123606558778129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="27">
-        <v>0.95433625694392898</v>
-      </c>
-      <c r="B19" s="27">
         <v>0.129508183359789</v>
       </c>
     </row>
